--- a/حسابداری/بانک ها/کشاورزی/1405/14050331-14050431.xlsx
+++ b/حسابداری/بانک ها/کشاورزی/1405/14050331-14050431.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\کشاورزی\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5677FA-56BF-48AB-9CE1-179CADABA7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1A6B64-D9AC-4867-A386-68E28BBD8838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,9 @@
         <v>201041045</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+      <c r="I5" s="9">
+        <v>125</v>
+      </c>
       <c r="J5" s="9">
         <v>195</v>
       </c>
